--- a/data/trans_orig/P6714-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6714-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se sienten comprometidos con su profesión en 2012</t>
+          <t>Población según si se sienten comprometidos con su profesión en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19563</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14309</t>
+          <t>13608</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36113</t>
+          <t>35427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19816</t>
+          <t>18909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>40627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67389</t>
+          <t>69205</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30431</t>
+          <t>29738</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52813</t>
+          <t>52064</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31817</t>
+          <t>32302</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48419</t>
+          <t>48787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78539</t>
+          <t>79067</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90465</t>
+          <t>92187</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119973</t>
+          <t>119842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70121</t>
+          <t>69080</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93943</t>
+          <t>93955</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170041</t>
+          <t>168632</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>205891</t>
+          <t>205159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,32%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25328</t>
+          <t>24115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24481</t>
+          <t>24127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21416</t>
+          <t>21096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43533</t>
+          <t>42937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21377</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44557</t>
+          <t>45370</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>18844</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41362</t>
+          <t>40881</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>45154</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79632</t>
+          <t>77497</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>117615</t>
+          <t>117553</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>161208</t>
+          <t>162421</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>81519</t>
+          <t>82923</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>119183</t>
+          <t>119589</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>209544</t>
+          <t>208190</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>266072</t>
+          <t>265651</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>202302</t>
+          <t>206022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>256043</t>
+          <t>258666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>154621</t>
+          <t>155151</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>198917</t>
+          <t>197913</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>371711</t>
+          <t>368398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>439109</t>
+          <t>439355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>470798</t>
+          <t>468141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>533301</t>
+          <t>530547</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224671</t>
+          <t>225975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274360</t>
+          <t>273831</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>716185</t>
+          <t>712862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>789585</t>
+          <t>793025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,42%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22324</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20130</t>
+          <t>19853</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43137</t>
+          <t>42418</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17535</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38955</t>
+          <t>38022</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43369</t>
+          <t>43269</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72739</t>
+          <t>73858</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>38244</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65793</t>
+          <t>66556</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30096</t>
+          <t>29872</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>55347</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74291</t>
+          <t>74222</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112773</t>
+          <t>111058</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>203852</t>
+          <t>202311</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236937</t>
+          <t>236987</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>144782</t>
+          <t>143994</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>176032</t>
+          <t>174471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>358385</t>
+          <t>356872</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>407274</t>
+          <t>402950</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,38%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15009</t>
+          <t>14179</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33807</t>
+          <t>32755</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10678</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28292</t>
+          <t>28467</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29335</t>
+          <t>29108</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>53801</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37501</t>
+          <t>37920</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66831</t>
+          <t>68301</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27020</t>
+          <t>28073</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53540</t>
+          <t>55460</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>72158</t>
+          <t>71756</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>113669</t>
+          <t>111642</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>164066</t>
+          <t>167108</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>218611</t>
+          <t>220798</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>132239</t>
+          <t>131838</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>182813</t>
+          <t>180126</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>311990</t>
+          <t>312585</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>383117</t>
+          <t>385609</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>286646</t>
+          <t>291303</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>354606</t>
+          <t>354108</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>213218</t>
+          <t>211912</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>269634</t>
+          <t>265827</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>515652</t>
+          <t>519535</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>601828</t>
+          <t>606485</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>788360</t>
+          <t>786549</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>865241</t>
+          <t>865987</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>456595</t>
+          <t>462604</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>523044</t>
+          <t>527322</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1269652</t>
+          <t>1271860</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1369432</t>
+          <t>1365579</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se sienten comprometidos con su profesión en 2016</t>
+          <t>Población según si se sienten comprometidos con su profesión en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16506</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16383</t>
+          <t>17219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28638</t>
+          <t>28615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21700</t>
+          <t>21426</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42768</t>
+          <t>42495</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13667</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28154</t>
+          <t>27179</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37697</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>63712</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31019</t>
+          <t>30585</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53351</t>
+          <t>53183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>23943</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46118</t>
+          <t>45488</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71716</t>
+          <t>71418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41334</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65673</t>
+          <t>64968</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17541</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33727</t>
+          <t>34344</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64290</t>
+          <t>65336</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>93271</t>
+          <t>93997</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>17708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38688</t>
+          <t>38920</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33062</t>
+          <t>32874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34258</t>
+          <t>36019</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63600</t>
+          <t>63504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37021</t>
+          <t>37133</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64671</t>
+          <t>64190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38196</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64562</t>
+          <t>65234</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81869</t>
+          <t>79635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>119219</t>
+          <t>117944</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>188668</t>
+          <t>190228</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>243173</t>
+          <t>243357</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>110129</t>
+          <t>108271</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>151644</t>
+          <t>149469</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>312437</t>
+          <t>313125</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>377446</t>
+          <t>378308</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239264</t>
+          <t>239670</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>292888</t>
+          <t>295141</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>193626</t>
+          <t>192418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>241482</t>
+          <t>240102</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>445004</t>
+          <t>444941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>519455</t>
+          <t>518889</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335787</t>
+          <t>341158</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>398777</t>
+          <t>401427</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211878</t>
+          <t>212681</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>263415</t>
+          <t>261917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>566412</t>
+          <t>565209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>645974</t>
+          <t>641340</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16594</t>
+          <t>17342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28530</t>
+          <t>27863</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22545</t>
+          <t>22043</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21661</t>
+          <t>20736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44351</t>
+          <t>44165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27029</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53609</t>
+          <t>51612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26419</t>
+          <t>26898</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49647</t>
+          <t>49100</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>60055</t>
+          <t>58664</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92112</t>
+          <t>92349</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57871</t>
+          <t>56150</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88780</t>
+          <t>89063</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44897</t>
+          <t>45044</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71634</t>
+          <t>72979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109430</t>
+          <t>109345</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>151889</t>
+          <t>150051</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>199438</t>
+          <t>202536</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239168</t>
+          <t>241970</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>177213</t>
+          <t>178771</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>211969</t>
+          <t>213786</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>389661</t>
+          <t>390898</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>438952</t>
+          <t>442322</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27821</t>
+          <t>26854</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54172</t>
+          <t>53934</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18706</t>
+          <t>18013</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41093</t>
+          <t>39174</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50823</t>
+          <t>50717</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84092</t>
+          <t>83977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59147</t>
+          <t>59273</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95019</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>57906</t>
+          <t>58650</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>91943</t>
+          <t>90477</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>126771</t>
+          <t>126515</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>176587</t>
+          <t>174117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>251552</t>
+          <t>254564</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>316346</t>
+          <t>317950</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>160701</t>
+          <t>161122</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>208853</t>
+          <t>209782</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>428609</t>
+          <t>429480</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>507958</t>
+          <t>511236</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>345302</t>
+          <t>345492</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>413699</t>
+          <t>414862</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>260048</t>
+          <t>263869</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>318342</t>
+          <t>321400</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>623511</t>
+          <t>624575</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>714717</t>
+          <t>715890</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>602441</t>
+          <t>607503</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>680497</t>
+          <t>679607</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>423692</t>
+          <t>425736</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>489310</t>
+          <t>489878</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1044914</t>
+          <t>1046129</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1151050</t>
+          <t>1152974</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6714-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6714-Estudios-trans_orig.xlsx
@@ -731,62 +731,62 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8905</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8806</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5381</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4834</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19823</t>
+          <t>19046</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28947</t>
+          <t>30574</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35427</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>19172</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38893</t>
+          <t>39228</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40627</t>
+          <t>40783</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69205</t>
+          <t>67699</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29738</t>
+          <t>29471</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52064</t>
+          <t>52185</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>13614</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32302</t>
+          <t>31944</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48787</t>
+          <t>47746</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79067</t>
+          <t>76736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92187</t>
+          <t>92178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119842</t>
+          <t>118490</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69080</t>
+          <t>70087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93955</t>
+          <t>95259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168632</t>
+          <t>169825</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>205159</t>
+          <t>207647</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>64,09%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24115</t>
+          <t>23798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24127</t>
+          <t>24296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42937</t>
+          <t>41460</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>21471</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45370</t>
+          <t>45003</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40881</t>
+          <t>40617</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45154</t>
+          <t>44744</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77497</t>
+          <t>77485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>117553</t>
+          <t>115185</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>162421</t>
+          <t>159672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82923</t>
+          <t>81133</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>119589</t>
+          <t>118034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>208190</t>
+          <t>208167</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>265651</t>
+          <t>264745</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>206022</t>
+          <t>205418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258666</t>
+          <t>257893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155151</t>
+          <t>155442</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>197913</t>
+          <t>200545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>368398</t>
+          <t>373356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>439355</t>
+          <t>445009</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>468141</t>
+          <t>470337</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>530547</t>
+          <t>532222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>225975</t>
+          <t>226643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273831</t>
+          <t>275665</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>712862</t>
+          <t>708381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>793025</t>
+          <t>787514</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,05%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12657</t>
+          <t>12634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14526</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>17323</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>13018</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19853</t>
+          <t>20333</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42418</t>
+          <t>42457</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17535</t>
+          <t>16473</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38022</t>
+          <t>38156</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43269</t>
+          <t>43090</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73858</t>
+          <t>73195</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38244</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66556</t>
+          <t>65644</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29872</t>
+          <t>29132</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55347</t>
+          <t>53921</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74222</t>
+          <t>74052</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111058</t>
+          <t>112143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202311</t>
+          <t>201578</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236987</t>
+          <t>238317</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>143994</t>
+          <t>144802</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>174471</t>
+          <t>176248</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>356872</t>
+          <t>355612</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>402950</t>
+          <t>402015</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,21%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14179</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32755</t>
+          <t>33718</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28467</t>
+          <t>27262</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29108</t>
+          <t>28348</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53801</t>
+          <t>53477</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37920</t>
+          <t>36906</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68301</t>
+          <t>66301</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28073</t>
+          <t>27688</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55460</t>
+          <t>56194</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>71756</t>
+          <t>72002</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>111642</t>
+          <t>112492</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>167108</t>
+          <t>169061</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>220798</t>
+          <t>221577</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>131838</t>
+          <t>133342</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>180126</t>
+          <t>182969</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>312585</t>
+          <t>308229</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>385609</t>
+          <t>382852</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>291303</t>
+          <t>291740</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>354108</t>
+          <t>353690</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>211912</t>
+          <t>211633</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>265827</t>
+          <t>266356</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>519535</t>
+          <t>518459</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>606485</t>
+          <t>602531</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>786549</t>
+          <t>787783</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>865987</t>
+          <t>861247</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>462604</t>
+          <t>463661</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>527322</t>
+          <t>524505</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1271860</t>
+          <t>1269407</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1365579</t>
+          <t>1369840</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,1%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>16523</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>16288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17219</t>
+          <t>17070</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11007</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28615</t>
+          <t>27174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21426</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42495</t>
+          <t>41756</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27179</t>
+          <t>27157</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38982</t>
+          <t>39052</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63712</t>
+          <t>65284</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>31721</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53183</t>
+          <t>54037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23943</t>
+          <t>24037</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45488</t>
+          <t>45480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71418</t>
+          <t>71419</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>40918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64968</t>
+          <t>66239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18214</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34344</t>
+          <t>32528</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65336</t>
+          <t>64341</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>93997</t>
+          <t>93424</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17708</t>
+          <t>17327</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38920</t>
+          <t>37374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13742</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32874</t>
+          <t>33672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36019</t>
+          <t>34265</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63504</t>
+          <t>63990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37133</t>
+          <t>36919</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64190</t>
+          <t>65496</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38196</t>
+          <t>38027</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65234</t>
+          <t>66082</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79635</t>
+          <t>81918</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117944</t>
+          <t>123864</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>190228</t>
+          <t>191948</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>243357</t>
+          <t>243429</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108271</t>
+          <t>108734</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>149469</t>
+          <t>150347</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>313125</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>378308</t>
+          <t>380516</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239670</t>
+          <t>234303</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>295141</t>
+          <t>292255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>192418</t>
+          <t>192858</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>240102</t>
+          <t>243198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>444941</t>
+          <t>444947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>518889</t>
+          <t>518047</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341158</t>
+          <t>340263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>401427</t>
+          <t>398073</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>212681</t>
+          <t>209735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>261917</t>
+          <t>260468</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>565209</t>
+          <t>568522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>641340</t>
+          <t>645857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17342</t>
+          <t>17081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9651</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27863</t>
+          <t>27587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22043</t>
+          <t>22092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20736</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44165</t>
+          <t>44777</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51612</t>
+          <t>51283</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26898</t>
+          <t>27258</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49100</t>
+          <t>48675</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58664</t>
+          <t>58110</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92349</t>
+          <t>92544</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56150</t>
+          <t>56907</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89063</t>
+          <t>86830</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45044</t>
+          <t>45117</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72979</t>
+          <t>74178</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109345</t>
+          <t>109907</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150051</t>
+          <t>153400</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202536</t>
+          <t>202045</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>241970</t>
+          <t>239159</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>178771</t>
+          <t>179317</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>213786</t>
+          <t>211951</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>390898</t>
+          <t>390517</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>442322</t>
+          <t>441381</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,97%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26854</t>
+          <t>25999</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53934</t>
+          <t>52328</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>17921</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39174</t>
+          <t>39342</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50717</t>
+          <t>51143</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83977</t>
+          <t>84631</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59273</t>
+          <t>60290</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95019</t>
+          <t>93762</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58650</t>
+          <t>57713</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>90477</t>
+          <t>91986</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>126515</t>
+          <t>128518</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>174117</t>
+          <t>175965</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>254564</t>
+          <t>253041</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>317950</t>
+          <t>315602</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>161122</t>
+          <t>160161</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>209782</t>
+          <t>212239</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>429480</t>
+          <t>436827</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>511236</t>
+          <t>510780</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>345492</t>
+          <t>345568</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>414862</t>
+          <t>414143</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6095,77 +6095,77 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>29,19%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>290337</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>261570</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>317419</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>28,1%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>25,31%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>30,72%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>668247</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>627096</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>717067</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>27,25%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>25,57%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>29,24%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>290337</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>263869</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>321400</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>28,1%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>25,54%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>31,1%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>668247</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>624575</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>715890</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>27,25%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>25,47%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>607503</t>
+          <t>603247</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>679607</t>
+          <t>678325</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>425736</t>
+          <t>424162</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>489878</t>
+          <t>490274</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1046129</t>
+          <t>1046095</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1152974</t>
+          <t>1147573</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
